--- a/docs/status/YBI_Verification_2025.xlsx
+++ b/docs/status/YBI_Verification_2025.xlsx
@@ -532,7 +532,7 @@
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>18 things the record has found and cannot resolve on its own. Every one was found by a control rather than by somebody reading. Every one is answerable from what you already know or can reach this week — nothing here needs counsel, an outside document, or a decision from a sponsor.</t>
+          <t>19 things the record has found and cannot resolve on its own. Every one was found by a control rather than by somebody reading. Every one is answerable from what you already know or can reach this week — nothing here needs counsel, an outside document, or a decision from a sponsor.</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1398,10 +1398,46 @@
       <c r="I19" s="11" t="inlineStr"/>
       <c r="J19" s="12" t="n"/>
     </row>
+    <row r="20" ht="74" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Invoices</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>The full invoice register does not exist. The system holds three invoices — 10018, 10023 and 10039, 57,961.42 between them. The 2025 ledger recognises America Makes revenue on four objectives: Drive AM 579,240.87, Digital Engineering 579,074.25, Last Tactical Mile 368,222.24 and Hybrid 191,638.05 — 1,718,175.41 in all.</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>4 objectives</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>Every invoice issued to NCDMM in 2025, across all four objectives.</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>A restatement is measured per invoice. With three on file the exercise can be demonstrated and not completed, and invoiced against recognised cannot be reconciled at all.</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr"/>
+      <c r="H20" s="11" t="inlineStr"/>
+      <c r="I20" s="11" t="inlineStr"/>
+      <c r="J20" s="12" t="n"/>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1" password="CC7A"/>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G58" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Pick one of: CONFIRMED — the record is right; CORRECTED — I have changed something; STILL CHECKING; SOMEBODY ELSE HAS TO ANSWER; NOT APPLICABLE. Leave it blank if you have not settled it." type="list">
+    <dataValidation sqref="G2:G59" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Pick one of: CONFIRMED — the record is right; CORRECTED — I have changed something; STILL CHECKING; SOMEBODY ELSE HAS TO ANSWER; NOT APPLICABLE. Leave it blank if you have not settled it." type="list">
       <formula1>'Choices'!$A$2:$A$6</formula1>
     </dataValidation>
   </dataValidations>
